--- a/data/raw/pubmed_query_results.xlsx
+++ b/data/raw/pubmed_query_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zacsentell/work/renal-genetic-testing-cea_v2/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4BDC1F-E9FA-5149-B672-C5D985E9B1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB433FD-CE9C-7F49-B8D5-4805EE3CC0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{36482912-1EB2-2645-8039-9AB186E00228}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="46080" windowHeight="25320" activeTab="1" xr2:uid="{36482912-1EB2-2645-8039-9AB186E00228}"/>
   </bookViews>
   <sheets>
     <sheet name="pubmed_query_results" sheetId="1" r:id="rId1"/>
@@ -2277,7 +2277,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3149,7 +3149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56771020-6714-E84A-8EBC-56D37C28F631}">
   <dimension ref="A1:H180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="45.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
@@ -3158,7 +3158,7 @@
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17">
+    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="34">
+    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>33532864</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="34">
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>37400792</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="17">
+    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>37261792</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="34">
+    <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>36573973</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="34">
+    <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>34264297</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="51">
+    <row r="7" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>33437033</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="51">
+    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>33226606</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="51">
+    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>37794564</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="34">
+    <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>32939031</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="51">
+    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>32450155</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="51">
+    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>35368817</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="51">
+    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>38972501</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="34">
+    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>38797326</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="34">
+    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>38104198</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="34">
+    <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>37126668</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="34">
+    <row r="17" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>38671320</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="34">
+    <row r="18" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>35229136</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17">
+    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>32739203</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="34">
+    <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>36753701</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="34">
+    <row r="21" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>35994232</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="51">
+    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>39138396</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="51">
+    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>34237823</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="34">
+    <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>34519781</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="34">
+    <row r="25" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>32646915</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="51">
+    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>38190104</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="68">
+    <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>36623684</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="34">
+    <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>36444934</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="51">
+    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>38852815</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="34">
+    <row r="30" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>37270787</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="34">
+    <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>35115544</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34">
+    <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32312792</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="34">
+    <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31853010</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="34">
+    <row r="34" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34067580</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="51">
+    <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>37624678</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="51">
+    <row r="36" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>37103770</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="51">
+    <row r="37" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>39405682</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="51">
+    <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>39402708</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="51">
+    <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37489581</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="51">
+    <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38905995</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="68">
+    <row r="41" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39819994</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="34">
+    <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>33783510</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="34">
+    <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>36245662</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="34">
+    <row r="44" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>32889981</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="34">
+    <row r="45" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>36525551</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="51">
+    <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>40345499</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="17">
+    <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>31822006</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="68">
+    <row r="48" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>40484353</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="34">
+    <row r="49" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>32799815</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="34">
+    <row r="50" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>36758113</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="34">
+    <row r="51" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>34449333</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="51">
+    <row r="52" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>35120996</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="34">
+    <row r="53" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>32855195</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="51">
+    <row r="54" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>34946851</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="51">
+    <row r="55" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>35006361</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="34">
+    <row r="56" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>34343338</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="34">
+    <row r="57" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>34363274</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="51">
+    <row r="58" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>37391705</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="51">
+    <row r="59" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>32080893</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="34">
+    <row r="60" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>33276865</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="51">
+    <row r="61" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>32574212</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="51">
+    <row r="62" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>37248651</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="85">
+    <row r="63" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>37510393</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="68">
+    <row r="64" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>40325148</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="51">
+    <row r="65" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>35962481</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="51">
+    <row r="66" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>36404353</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="68">
+    <row r="67" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>36072369</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="51">
+    <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>35099770</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="68">
+    <row r="69" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>35393322</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="51">
+    <row r="70" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>35148957</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="51">
+    <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>39054238</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="51">
+    <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>33838163</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="34">
+    <row r="73" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>37229630</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="51">
+    <row r="74" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>36949158</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="51">
+    <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>37759214</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="68">
+    <row r="76" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>39965361</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="51">
+    <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>37978231</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="51">
+    <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>37037154</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="68">
+    <row r="79" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>38022507</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="51">
+    <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>34354814</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="51">
+    <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>36627639</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="51">
+    <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>33108403</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="51">
+    <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>38152017</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="34">
+    <row r="84" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>35603906</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="51">
+    <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>33095447</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="68">
+    <row r="86" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>34521993</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="34">
+    <row r="87" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>36688940</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="68">
+    <row r="88" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>35980750</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="51">
+    <row r="89" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>34946941</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="51">
+    <row r="90" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>31646670</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="51">
+    <row r="91" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>34545573</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="51">
+    <row r="92" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>39333970</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="68">
+    <row r="93" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>34134020</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="51">
+    <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>34565606</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="51">
+    <row r="95" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>32029730</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="68">
+    <row r="96" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>35064937</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="68">
+    <row r="97" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>36463540</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="51">
+    <row r="98" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>32398770</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="17">
+    <row r="99" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>33958773</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="68">
+    <row r="100" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>38347632</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="51">
+    <row r="101" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>34148064</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="34">
+    <row r="102" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>34327334</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="51">
+    <row r="103" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>37042117</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="51">
+    <row r="104" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>39150521</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="51">
+    <row r="105" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>35369652</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="34">
+    <row r="106" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>38906652</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="51">
+    <row r="107" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>35244702</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="51">
+    <row r="108" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>39363241</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="34">
+    <row r="109" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>32299846</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="51">
+    <row r="110" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>32779812</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="51">
+    <row r="111" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>39626636</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="68">
+    <row r="112" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>38932496</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="68">
+    <row r="113" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>33407230</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="34">
+    <row r="114" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>37864521</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="68">
+    <row r="115" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>33693791</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="51">
+    <row r="116" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>32969247</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="68">
+    <row r="117" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>35429337</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="51">
+    <row r="118" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>38547852</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="68">
+    <row r="119" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>39143076</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="68">
+    <row r="120" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>37228720</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="34">
+    <row r="121" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>34628264</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="68">
+    <row r="122" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>36547129</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="51">
+    <row r="123" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>40533884</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="68">
+    <row r="124" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>34923958</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="34">
+    <row r="125" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>39832277</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="51">
+    <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>31999492</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="34">
+    <row r="127" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>32723786</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="68">
+    <row r="128" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>33107440</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="102">
+    <row r="129" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>30953057</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="68">
+    <row r="130" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>37468236</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="34">
+    <row r="131" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>32803290</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="85">
+    <row r="132" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>38609702</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="68">
+    <row r="133" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>32600054</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="34">
+    <row r="134" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>32828237</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="85">
+    <row r="135" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>39107157</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="34">
+    <row r="136" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>33534524</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="68">
+    <row r="137" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>34197840</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="51">
+    <row r="138" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>32334565</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="51">
+    <row r="139" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>36782285</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="68">
+    <row r="140" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>35314744</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="51">
+    <row r="141" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>38574989</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="51">
+    <row r="142" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>31852011</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="51">
+    <row r="143" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>33107222</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="51">
+    <row r="144" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>31992108</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="51">
+    <row r="145" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>32661119</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="51">
+    <row r="146" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>38678107</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="34">
+    <row r="147" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>37574436</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="68">
+    <row r="148" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>34237133</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="34">
+    <row r="149" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>33087822</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="68">
+    <row r="150" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>33861738</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="51">
+    <row r="151" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>33048330</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="68">
+    <row r="152" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>32673684</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="51">
+    <row r="153" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>35977080</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="85">
+    <row r="154" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>38886300</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="68">
+    <row r="155" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>34358382</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="51">
+    <row r="156" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>34654685</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="51">
+    <row r="157" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>32176594</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="51">
+    <row r="158" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>39913368</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="51">
+    <row r="159" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>37349938</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="68">
+    <row r="160" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31764220</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="34">
+    <row r="161" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>36253912</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="68">
+    <row r="162" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>35763031</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="85">
+    <row r="163" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>35655039</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="51">
+    <row r="164" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>35264217</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="51">
+    <row r="165" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>33111320</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="68">
+    <row r="166" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>32968206</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="51">
+    <row r="167" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>31513279</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="85">
+    <row r="168" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>37358729</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="51">
+    <row r="169" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>35017463</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="51">
+    <row r="170" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>38032814</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="51">
+    <row r="171" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>32060504</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="51">
+    <row r="172" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>34980496</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="68">
+    <row r="173" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>38327067</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="51">
+    <row r="174" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>36292688</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="51">
+    <row r="175" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>32659871</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="17">
+    <row r="176" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>32358593</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="51">
+    <row r="177" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>38752978</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="34">
+    <row r="178" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>33275263</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="51">
+    <row r="179" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>32211780</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="51">
+    <row r="180" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>34558169</v>
       </c>
@@ -6293,7 +6293,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73CCE44A-5414-404E-A419-00AC61B8F7E5}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:N180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
@@ -6308,7 +6308,7 @@
     <col min="14" max="14" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="34" hidden="1">
+    <row r="2" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>33532864</v>
       </c>
@@ -6371,7 +6371,7 @@
       <c r="L2"/>
       <c r="M2"/>
     </row>
-    <row r="3" spans="1:14" ht="17" hidden="1">
+    <row r="3" spans="1:14" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>37400792</v>
       </c>
@@ -6390,7 +6390,7 @@
       <c r="L3"/>
       <c r="M3"/>
     </row>
-    <row r="4" spans="1:14" ht="17" hidden="1">
+    <row r="4" spans="1:14" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>37261792</v>
       </c>
@@ -6409,7 +6409,7 @@
       <c r="L4"/>
       <c r="M4"/>
     </row>
-    <row r="5" spans="1:14" ht="34" hidden="1">
+    <row r="5" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>36573973</v>
       </c>
@@ -6431,7 +6431,7 @@
       <c r="L5"/>
       <c r="M5"/>
     </row>
-    <row r="6" spans="1:14" ht="34" hidden="1">
+    <row r="6" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>34264297</v>
       </c>
@@ -6450,7 +6450,7 @@
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:14" ht="34" hidden="1">
+    <row r="7" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>33437033</v>
       </c>
@@ -6472,7 +6472,7 @@
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:14" ht="51">
+    <row r="8" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>33226606</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="H8" t="s">
         <v>473</v>
@@ -6513,7 +6513,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="119">
+    <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>37794564</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="34">
+    <row r="10" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>32939031</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="51" hidden="1">
+    <row r="11" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>32450155</v>
       </c>
@@ -6623,7 +6623,7 @@
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:14" ht="51" hidden="1">
+    <row r="12" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>35368817</v>
       </c>
@@ -6645,7 +6645,7 @@
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:14" ht="34">
+    <row r="13" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>38972501</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="34" hidden="1">
+    <row r="14" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>38797326</v>
       </c>
@@ -6705,7 +6705,7 @@
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="1:14" ht="34" hidden="1">
+    <row r="15" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>38104198</v>
       </c>
@@ -6724,7 +6724,7 @@
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="1:14" ht="34" hidden="1">
+    <row r="16" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>37126668</v>
       </c>
@@ -6743,7 +6743,7 @@
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="1:14" ht="34" hidden="1">
+    <row r="17" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>38671320</v>
       </c>
@@ -6762,7 +6762,7 @@
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="1:14" ht="34" hidden="1">
+    <row r="18" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>35229136</v>
       </c>
@@ -6781,7 +6781,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="1:14" ht="17">
+    <row r="19" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>32739203</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="34">
+    <row r="20" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>36753701</v>
       </c>
@@ -6839,7 +6839,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="34" hidden="1">
+    <row r="21" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>35994232</v>
       </c>
@@ -6858,7 +6858,7 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="1:14" ht="34" hidden="1">
+    <row r="22" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>39138396</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="1:14" ht="34" hidden="1">
+    <row r="23" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>34237823</v>
       </c>
@@ -6899,7 +6899,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:14" ht="34" hidden="1">
+    <row r="24" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>34519781</v>
       </c>
@@ -6918,7 +6918,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:14" ht="34">
+    <row r="25" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>32646915</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="51" hidden="1">
+    <row r="26" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>38190104</v>
       </c>
@@ -6963,7 +6963,7 @@
       <c r="L26"/>
       <c r="M26"/>
     </row>
-    <row r="27" spans="1:14" ht="51" hidden="1">
+    <row r="27" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>36623684</v>
       </c>
@@ -6982,7 +6982,7 @@
       <c r="L27"/>
       <c r="M27"/>
     </row>
-    <row r="28" spans="1:14" ht="34" hidden="1">
+    <row r="28" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>36444934</v>
       </c>
@@ -7001,7 +7001,7 @@
       <c r="L28"/>
       <c r="M28"/>
     </row>
-    <row r="29" spans="1:14" ht="51" hidden="1">
+    <row r="29" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>38852815</v>
       </c>
@@ -7020,7 +7020,7 @@
       <c r="L29"/>
       <c r="M29"/>
     </row>
-    <row r="30" spans="1:14" ht="34">
+    <row r="30" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>37270787</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="34" hidden="1">
+    <row r="31" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>35115544</v>
       </c>
@@ -7071,7 +7071,7 @@
       <c r="L31"/>
       <c r="M31"/>
     </row>
-    <row r="32" spans="1:14" ht="34" hidden="1">
+    <row r="32" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>32312792</v>
       </c>
@@ -7093,7 +7093,7 @@
       <c r="L32"/>
       <c r="M32"/>
     </row>
-    <row r="33" spans="1:14" ht="34" hidden="1">
+    <row r="33" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31853010</v>
       </c>
@@ -7112,7 +7112,7 @@
       <c r="L33"/>
       <c r="M33"/>
     </row>
-    <row r="34" spans="1:14" ht="34" hidden="1">
+    <row r="34" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>34067580</v>
       </c>
@@ -7131,7 +7131,7 @@
       <c r="L34"/>
       <c r="M34"/>
     </row>
-    <row r="35" spans="1:14" ht="51" hidden="1">
+    <row r="35" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>37624678</v>
       </c>
@@ -7150,7 +7150,7 @@
       <c r="L35"/>
       <c r="M35"/>
     </row>
-    <row r="36" spans="1:14" ht="34" hidden="1">
+    <row r="36" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>37103770</v>
       </c>
@@ -7169,7 +7169,7 @@
       <c r="L36"/>
       <c r="M36"/>
     </row>
-    <row r="37" spans="1:14" ht="51" hidden="1">
+    <row r="37" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>39405682</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="L37"/>
       <c r="M37"/>
     </row>
-    <row r="38" spans="1:14" ht="51" hidden="1">
+    <row r="38" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>39402708</v>
       </c>
@@ -7207,7 +7207,7 @@
       <c r="L38"/>
       <c r="M38"/>
     </row>
-    <row r="39" spans="1:14" ht="34">
+    <row r="39" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37489581</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="51" hidden="1">
+    <row r="40" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38905995</v>
       </c>
@@ -7252,7 +7252,7 @@
       <c r="L40"/>
       <c r="M40"/>
     </row>
-    <row r="41" spans="1:14" ht="51" hidden="1">
+    <row r="41" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39819994</v>
       </c>
@@ -7271,7 +7271,7 @@
       <c r="L41"/>
       <c r="M41"/>
     </row>
-    <row r="42" spans="1:14" ht="34" hidden="1">
+    <row r="42" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>33783510</v>
       </c>
@@ -7290,7 +7290,7 @@
       <c r="L42"/>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:14" ht="34" hidden="1">
+    <row r="43" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>36245662</v>
       </c>
@@ -7309,7 +7309,7 @@
       <c r="L43"/>
       <c r="M43"/>
     </row>
-    <row r="44" spans="1:14" ht="34" hidden="1">
+    <row r="44" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>32889981</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="L44"/>
       <c r="M44"/>
     </row>
-    <row r="45" spans="1:14" ht="34" hidden="1">
+    <row r="45" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>36525551</v>
       </c>
@@ -7347,7 +7347,7 @@
       <c r="L45"/>
       <c r="M45"/>
     </row>
-    <row r="46" spans="1:14" ht="51" hidden="1">
+    <row r="46" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>40345499</v>
       </c>
@@ -7366,7 +7366,7 @@
       <c r="L46"/>
       <c r="M46"/>
     </row>
-    <row r="47" spans="1:14" ht="17" hidden="1">
+    <row r="47" spans="1:14" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>31822006</v>
       </c>
@@ -7385,7 +7385,7 @@
       <c r="L47"/>
       <c r="M47"/>
     </row>
-    <row r="48" spans="1:14" ht="68" hidden="1">
+    <row r="48" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>40484353</v>
       </c>
@@ -7404,7 +7404,7 @@
       <c r="L48"/>
       <c r="M48"/>
     </row>
-    <row r="49" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="49" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>32799815</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="50" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="50" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>36758113</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="51" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>34449333</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="52" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="52" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>35120996</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="53" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="53" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>32855195</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="54" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="54" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>34946851</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="55" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="55" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>35006361</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="56" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="56" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>34343338</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="57" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="57" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>34363274</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="58" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="58" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>37391705</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="59" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="59" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>32080893</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="60" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="60" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>33276865</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="61" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="61" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>32574212</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="62" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="62" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>37248651</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="63" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="63" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>37510393</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="64" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="64" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>40325148</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="51" hidden="1">
+    <row r="65" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>35962481</v>
       </c>
@@ -7695,7 +7695,7 @@
       <c r="L65"/>
       <c r="M65"/>
     </row>
-    <row r="66" spans="1:14" ht="51" hidden="1">
+    <row r="66" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>36404353</v>
       </c>
@@ -7714,7 +7714,7 @@
       <c r="L66"/>
       <c r="M66"/>
     </row>
-    <row r="67" spans="1:14" ht="51" hidden="1">
+    <row r="67" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>36072369</v>
       </c>
@@ -7733,7 +7733,7 @@
       <c r="L67"/>
       <c r="M67"/>
     </row>
-    <row r="68" spans="1:14" ht="68">
+    <row r="68" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>35099770</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="51">
+    <row r="69" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>35393322</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="51" hidden="1">
+    <row r="70" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>35148957</v>
       </c>
@@ -7825,7 +7825,7 @@
       <c r="L70"/>
       <c r="M70"/>
     </row>
-    <row r="71" spans="1:14" ht="34" hidden="1">
+    <row r="71" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>39054238</v>
       </c>
@@ -7844,7 +7844,7 @@
       <c r="L71"/>
       <c r="M71"/>
     </row>
-    <row r="72" spans="1:14" ht="34" hidden="1">
+    <row r="72" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>33838163</v>
       </c>
@@ -7863,7 +7863,7 @@
       <c r="L72"/>
       <c r="M72"/>
     </row>
-    <row r="73" spans="1:14" ht="34" hidden="1">
+    <row r="73" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>37229630</v>
       </c>
@@ -7882,7 +7882,7 @@
       <c r="L73"/>
       <c r="M73"/>
     </row>
-    <row r="74" spans="1:14" ht="51" hidden="1">
+    <row r="74" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>36949158</v>
       </c>
@@ -7901,7 +7901,7 @@
       <c r="L74"/>
       <c r="M74"/>
     </row>
-    <row r="75" spans="1:14" ht="51" hidden="1">
+    <row r="75" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>37759214</v>
       </c>
@@ -7920,7 +7920,7 @@
       <c r="L75"/>
       <c r="M75"/>
     </row>
-    <row r="76" spans="1:14" ht="51" hidden="1">
+    <row r="76" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>39965361</v>
       </c>
@@ -7939,7 +7939,7 @@
       <c r="L76"/>
       <c r="M76"/>
     </row>
-    <row r="77" spans="1:14" ht="51" hidden="1">
+    <row r="77" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>37978231</v>
       </c>
@@ -7958,7 +7958,7 @@
       <c r="L77"/>
       <c r="M77"/>
     </row>
-    <row r="78" spans="1:14" ht="51" hidden="1">
+    <row r="78" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>37037154</v>
       </c>
@@ -7977,7 +7977,7 @@
       <c r="L78"/>
       <c r="M78"/>
     </row>
-    <row r="79" spans="1:14" ht="68" hidden="1">
+    <row r="79" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>38022507</v>
       </c>
@@ -7996,7 +7996,7 @@
       <c r="L79"/>
       <c r="M79"/>
     </row>
-    <row r="80" spans="1:14" ht="51" hidden="1">
+    <row r="80" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>34354814</v>
       </c>
@@ -8015,7 +8015,7 @@
       <c r="L80"/>
       <c r="M80"/>
     </row>
-    <row r="81" spans="1:14" ht="51" hidden="1">
+    <row r="81" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>36627639</v>
       </c>
@@ -8034,7 +8034,7 @@
       <c r="L81"/>
       <c r="M81"/>
     </row>
-    <row r="82" spans="1:14" ht="51" hidden="1">
+    <row r="82" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>33108403</v>
       </c>
@@ -8053,7 +8053,7 @@
       <c r="L82"/>
       <c r="M82"/>
     </row>
-    <row r="83" spans="1:14" ht="51" hidden="1">
+    <row r="83" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>38152017</v>
       </c>
@@ -8072,7 +8072,7 @@
       <c r="L83"/>
       <c r="M83"/>
     </row>
-    <row r="84" spans="1:14" ht="34" hidden="1">
+    <row r="84" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>35603906</v>
       </c>
@@ -8091,7 +8091,7 @@
       <c r="L84"/>
       <c r="M84"/>
     </row>
-    <row r="85" spans="1:14" ht="34">
+    <row r="85" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>33095447</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="51" hidden="1">
+    <row r="86" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>34521993</v>
       </c>
@@ -8136,7 +8136,7 @@
       <c r="L86"/>
       <c r="M86"/>
     </row>
-    <row r="87" spans="1:14" ht="34" hidden="1">
+    <row r="87" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>36688940</v>
       </c>
@@ -8155,7 +8155,7 @@
       <c r="L87"/>
       <c r="M87"/>
     </row>
-    <row r="88" spans="1:14" ht="68" hidden="1">
+    <row r="88" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>35980750</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="L88"/>
       <c r="M88"/>
     </row>
-    <row r="89" spans="1:14" ht="51" hidden="1">
+    <row r="89" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>34946941</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="L89"/>
       <c r="M89"/>
     </row>
-    <row r="90" spans="1:14" ht="51" hidden="1">
+    <row r="90" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>31646670</v>
       </c>
@@ -8212,7 +8212,7 @@
       <c r="L90"/>
       <c r="M90"/>
     </row>
-    <row r="91" spans="1:14" ht="34" hidden="1">
+    <row r="91" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>34545573</v>
       </c>
@@ -8231,7 +8231,7 @@
       <c r="L91"/>
       <c r="M91"/>
     </row>
-    <row r="92" spans="1:14" ht="51" hidden="1">
+    <row r="92" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>39333970</v>
       </c>
@@ -8250,7 +8250,7 @@
       <c r="L92"/>
       <c r="M92"/>
     </row>
-    <row r="93" spans="1:14" ht="51" hidden="1">
+    <row r="93" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>34134020</v>
       </c>
@@ -8269,7 +8269,7 @@
       <c r="L93"/>
       <c r="M93"/>
     </row>
-    <row r="94" spans="1:14" ht="51" hidden="1">
+    <row r="94" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>34565606</v>
       </c>
@@ -8288,7 +8288,7 @@
       <c r="L94"/>
       <c r="M94"/>
     </row>
-    <row r="95" spans="1:14" ht="34" hidden="1">
+    <row r="95" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>32029730</v>
       </c>
@@ -8307,7 +8307,7 @@
       <c r="L95"/>
       <c r="M95"/>
     </row>
-    <row r="96" spans="1:14" ht="51" hidden="1">
+    <row r="96" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>35064937</v>
       </c>
@@ -8326,7 +8326,7 @@
       <c r="L96"/>
       <c r="M96"/>
     </row>
-    <row r="97" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="97" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>36463540</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="98" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="98" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>32398770</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="99" spans="1:5" customFormat="1" ht="17" hidden="1">
+    <row r="99" spans="1:5" customFormat="1" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>33958773</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="100" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="100" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>38347632</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="101" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>34148064</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="102" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="102" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>34327334</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="103" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="103" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>37042117</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="104" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>39150521</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="105" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>35369652</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="106" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="106" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>38906652</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="107" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>35244702</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="108" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="108" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>39363241</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="109" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>32299846</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="110" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="110" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>32779812</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="111" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="111" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>39626636</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="112" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>38932496</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="51" hidden="1">
+    <row r="113" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>33407230</v>
       </c>
@@ -8617,7 +8617,7 @@
       <c r="L113"/>
       <c r="M113"/>
     </row>
-    <row r="114" spans="1:14" ht="34" hidden="1">
+    <row r="114" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>37864521</v>
       </c>
@@ -8636,7 +8636,7 @@
       <c r="L114"/>
       <c r="M114"/>
     </row>
-    <row r="115" spans="1:14" ht="68" hidden="1">
+    <row r="115" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>33693791</v>
       </c>
@@ -8655,7 +8655,7 @@
       <c r="L115"/>
       <c r="M115"/>
     </row>
-    <row r="116" spans="1:14" ht="34" hidden="1">
+    <row r="116" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>32969247</v>
       </c>
@@ -8674,7 +8674,7 @@
       <c r="L116"/>
       <c r="M116"/>
     </row>
-    <row r="117" spans="1:14" ht="68" hidden="1">
+    <row r="117" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>35429337</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="L117"/>
       <c r="M117"/>
     </row>
-    <row r="118" spans="1:14" ht="51" hidden="1">
+    <row r="118" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>38547852</v>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="L118"/>
       <c r="M118"/>
     </row>
-    <row r="119" spans="1:14" ht="51" hidden="1">
+    <row r="119" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>39143076</v>
       </c>
@@ -8731,7 +8731,7 @@
       <c r="L119"/>
       <c r="M119"/>
     </row>
-    <row r="120" spans="1:14" ht="68" hidden="1">
+    <row r="120" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>37228720</v>
       </c>
@@ -8750,7 +8750,7 @@
       <c r="L120"/>
       <c r="M120"/>
     </row>
-    <row r="121" spans="1:14" ht="34" hidden="1">
+    <row r="121" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>34628264</v>
       </c>
@@ -8769,7 +8769,7 @@
       <c r="L121"/>
       <c r="M121"/>
     </row>
-    <row r="122" spans="1:14" ht="51" hidden="1">
+    <row r="122" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>36547129</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="L122"/>
       <c r="M122"/>
     </row>
-    <row r="123" spans="1:14" ht="51">
+    <row r="123" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>40533884</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="68" hidden="1">
+    <row r="124" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>34923958</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="L124"/>
       <c r="M124"/>
     </row>
-    <row r="125" spans="1:14" ht="34" hidden="1">
+    <row r="125" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>39832277</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="L125"/>
       <c r="M125"/>
     </row>
-    <row r="126" spans="1:14" ht="51" hidden="1">
+    <row r="126" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>31999492</v>
       </c>
@@ -8889,7 +8889,7 @@
       <c r="L126"/>
       <c r="M126"/>
     </row>
-    <row r="127" spans="1:14" ht="34" hidden="1">
+    <row r="127" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>32723786</v>
       </c>
@@ -8908,7 +8908,7 @@
       <c r="L127"/>
       <c r="M127"/>
     </row>
-    <row r="128" spans="1:14" ht="51" hidden="1">
+    <row r="128" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>33107440</v>
       </c>
@@ -8927,7 +8927,7 @@
       <c r="L128"/>
       <c r="M128"/>
     </row>
-    <row r="129" spans="1:5" customFormat="1" ht="85" hidden="1">
+    <row r="129" spans="1:5" customFormat="1" ht="85" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>30953057</v>
       </c>
@@ -8944,7 +8944,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="130" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="130" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>37468236</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="131" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="131" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>32803290</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="132" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="132" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>38609702</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="133" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="133" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>32600054</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="134" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="134" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>32828237</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="135" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="135" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>39107157</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="136" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="136" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>33534524</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="137" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="137" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>34197840</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="138" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="138" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>32334565</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="139" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="139" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>36782285</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="140" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="140" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>35314744</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="141" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="141" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>38574989</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="142" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="142" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>31852011</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="143" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="143" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>33107222</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="144" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="144" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>31992108</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="145" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="145" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>32661119</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="146" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="146" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>38678107</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="147" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="147" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>37574436</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="148" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="148" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>34237133</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="149" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="149" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>33087822</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="150" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="150" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>33861738</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="151" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="151" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>33048330</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="152" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="152" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>32673684</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="153" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="153" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>35977080</v>
       </c>
@@ -9352,7 +9352,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="154" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="154" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>38886300</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="155" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="155" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>34358382</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="156" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="156" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>34654685</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="157" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="157" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>32176594</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="158" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="158" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>39913368</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="159" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="159" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>37349938</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="160" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="160" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31764220</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="161" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="161" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>36253912</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="162" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="162" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>35763031</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="163" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="163" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>35655039</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="164" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="164" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>35264217</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="165" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="165" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>33111320</v>
       </c>
@@ -9556,7 +9556,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="166" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="166" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>32968206</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="167" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="167" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>31513279</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="168" spans="1:5" customFormat="1" ht="68" hidden="1">
+    <row r="168" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>37358729</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="169" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="169" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>35017463</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="170" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="170" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>38032814</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="171" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="171" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>32060504</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="172" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="172" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>34980496</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="173" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="173" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>38327067</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="174" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="174" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>36292688</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="175" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="175" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>32659871</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="176" spans="1:5" customFormat="1" ht="17" hidden="1">
+    <row r="176" spans="1:5" customFormat="1" ht="17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>32358593</v>
       </c>
@@ -9743,7 +9743,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="177" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="177" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>38752978</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="178" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="178" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>33275263</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="179" spans="1:5" customFormat="1" ht="51" hidden="1">
+    <row r="179" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>32211780</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="180" spans="1:5" customFormat="1" ht="34" hidden="1">
+    <row r="180" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>34558169</v>
       </c>
@@ -9826,14 +9826,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23894E8A-015E-5545-964F-589B1BE15133}">
   <dimension ref="A1:L180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="50.5" customWidth="1"/>
     <col min="9" max="9" width="11.6640625" customWidth="1"/>
     <col min="10" max="10" width="33.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>510</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>33532864</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>37400792</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>37261792</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>34264297</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>38797326</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>38104198</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>37126668</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>38671320</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>35229136</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>35994232</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>39138396</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>34519781</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>38190104</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>36623684</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>36444934</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>38852815</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>35115544</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>31853010</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>34067580</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>37624678</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>37103770</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>39405682</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>39402708</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>38905995</v>
       </c>
@@ -10663,7 +10663,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>39819994</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>33783510</v>
       </c>
@@ -10729,7 +10729,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>36245662</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>32889981</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>36525551</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>40345499</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31822006</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>40484353</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32799815</v>
       </c>
@@ -10960,7 +10960,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>36758113</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34449333</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35120996</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>32855195</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>34946851</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>35006361</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>34343338</v>
       </c>
@@ -11191,7 +11191,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>34363274</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>37391705</v>
       </c>
@@ -11257,7 +11257,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>32080893</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>33276865</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>32574212</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>37248651</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>37510393</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>40325148</v>
       </c>
@@ -11455,7 +11455,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>35962481</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>36404353</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>36072369</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>35148957</v>
       </c>
@@ -11587,7 +11587,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>39054238</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>33838163</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>37229630</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>36949158</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>37759214</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>39965361</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>37978231</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>37037154</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>38022507</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>34354814</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>36627639</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>33108403</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>38152017</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>35603906</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>34521993</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>36688940</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>35980750</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>34946941</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>31646670</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>34545573</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>39333970</v>
       </c>
@@ -12280,7 +12280,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>34134020</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>34565606</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>32029730</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>35064937</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>36463540</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>32398770</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>33958773</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>38347632</v>
       </c>
@@ -12544,7 +12544,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>34148064</v>
       </c>
@@ -12577,7 +12577,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>34327334</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>37042117</v>
       </c>
@@ -12643,7 +12643,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>39150521</v>
       </c>
@@ -12676,7 +12676,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>35369652</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>38906652</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>35244702</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>39363241</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>32299846</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>32779812</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>39626636</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>38932496</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>33407230</v>
       </c>
@@ -12973,7 +12973,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>37864521</v>
       </c>
@@ -13006,7 +13006,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>33693791</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>32969247</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>35429337</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>38547852</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>39143076</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>37228720</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>34628264</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>36547129</v>
       </c>
@@ -13270,7 +13270,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>34923958</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>39832277</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>31999492</v>
       </c>
@@ -13369,7 +13369,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>32723786</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>33107440</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>30953057</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>37468236</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>32803290</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>38609702</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>32600054</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>32828237</v>
       </c>
@@ -13633,7 +13633,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>39107157</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>33534524</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>34197840</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>32334565</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>36782285</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>35314744</v>
       </c>
@@ -13831,7 +13831,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>38574989</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>31852011</v>
       </c>
@@ -13897,7 +13897,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>33107222</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>31992108</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>32661119</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>38678107</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>37574436</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>34237133</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>33087822</v>
       </c>
@@ -14128,7 +14128,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>33861738</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>33048330</v>
       </c>
@@ -14194,7 +14194,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>32673684</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>35977080</v>
       </c>
@@ -14260,7 +14260,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>38886300</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>34358382</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>34654685</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>32176594</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>39913368</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>37349938</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>31764220</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>36253912</v>
       </c>
@@ -14524,7 +14524,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>35763031</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>35655039</v>
       </c>
@@ -14590,7 +14590,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>35264217</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>33111320</v>
       </c>
@@ -14656,7 +14656,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>32968206</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>31513279</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>37358729</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>35017463</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>38032814</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>32060504</v>
       </c>
@@ -14854,7 +14854,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>34980496</v>
       </c>
@@ -14887,7 +14887,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>38327067</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>36292688</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>32659871</v>
       </c>
@@ -14986,7 +14986,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>32358593</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>38752978</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>33275263</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>32211780</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>34558169</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>36573973</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>33437033</v>
       </c>
@@ -15221,7 +15221,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>32450155</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>35368817</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>34237823</v>
       </c>
@@ -15326,15 +15326,15 @@
         <v>546</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>33226606</v>
+        <v>32312792</v>
       </c>
       <c r="B167" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="C167">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D167" t="s">
         <v>522</v>
@@ -15343,7 +15343,7 @@
         <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -15352,21 +15352,24 @@
         <v>1</v>
       </c>
       <c r="I167" t="s">
-        <v>527</v>
+        <v>523</v>
+      </c>
+      <c r="J167" t="s">
+        <v>705</v>
       </c>
       <c r="K167" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>37794564</v>
+        <v>32739203</v>
       </c>
       <c r="B168" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C168">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D168" t="s">
         <v>522</v>
@@ -15384,24 +15387,27 @@
         <v>1</v>
       </c>
       <c r="I168" t="s">
-        <v>527</v>
+        <v>523</v>
+      </c>
+      <c r="J168" t="s">
+        <v>706</v>
       </c>
       <c r="K168" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="L168" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169">
-        <v>32939031</v>
+        <v>36753701</v>
       </c>
       <c r="B169" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C169">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D169" t="s">
         <v>522</v>
@@ -15419,24 +15425,27 @@
         <v>1</v>
       </c>
       <c r="I169" t="s">
-        <v>527</v>
+        <v>523</v>
+      </c>
+      <c r="J169" t="s">
+        <v>705</v>
       </c>
       <c r="K169" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="L169" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>38972501</v>
+        <v>32646915</v>
       </c>
       <c r="B170" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="C170">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D170" t="s">
         <v>522</v>
@@ -15454,21 +15463,27 @@
         <v>1</v>
       </c>
       <c r="I170" t="s">
-        <v>527</v>
+        <v>523</v>
+      </c>
+      <c r="J170" t="s">
+        <v>706</v>
       </c>
       <c r="K170" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12">
+        <v>548</v>
+      </c>
+      <c r="L170" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>32739203</v>
+        <v>37270787</v>
       </c>
       <c r="B171" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C171">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D171" t="s">
         <v>522</v>
@@ -15489,21 +15504,21 @@
         <v>523</v>
       </c>
       <c r="J171" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="K171" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="L171" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>36753701</v>
+        <v>37489581</v>
       </c>
       <c r="B172" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C172">
         <v>2023</v>
@@ -15518,33 +15533,33 @@
         <v>527</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="s">
         <v>523</v>
       </c>
       <c r="J172" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="K172" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="L172" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173">
-        <v>32646915</v>
+        <v>35393322</v>
       </c>
       <c r="B173" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="C173">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D173" t="s">
         <v>522</v>
@@ -15568,21 +15583,21 @@
         <v>706</v>
       </c>
       <c r="K173" t="s">
-        <v>548</v>
+        <v>592</v>
       </c>
       <c r="L173" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174">
-        <v>37270787</v>
+        <v>33095447</v>
       </c>
       <c r="B174" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="C174">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D174" t="s">
         <v>522</v>
@@ -15603,24 +15618,24 @@
         <v>523</v>
       </c>
       <c r="J174" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="K174" t="s">
-        <v>553</v>
+        <v>608</v>
       </c>
       <c r="L174" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175">
-        <v>32312792</v>
+        <v>33226606</v>
       </c>
       <c r="B175" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="C175">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D175" t="s">
         <v>522</v>
@@ -15638,21 +15653,18 @@
         <v>1</v>
       </c>
       <c r="I175" t="s">
-        <v>523</v>
-      </c>
-      <c r="J175" t="s">
-        <v>705</v>
+        <v>527</v>
       </c>
       <c r="K175" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176">
-        <v>37489581</v>
+        <v>37794564</v>
       </c>
       <c r="B176" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="C176">
         <v>2023</v>
@@ -15673,27 +15685,24 @@
         <v>1</v>
       </c>
       <c r="I176" t="s">
-        <v>523</v>
-      </c>
-      <c r="J176" t="s">
-        <v>705</v>
+        <v>527</v>
       </c>
       <c r="K176" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="L176" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177">
-        <v>35099770</v>
+        <v>32939031</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="C177">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D177" t="s">
         <v>522</v>
@@ -15714,21 +15723,21 @@
         <v>527</v>
       </c>
       <c r="K177" t="s">
-        <v>591</v>
+        <v>533</v>
       </c>
       <c r="L177" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178">
-        <v>35393322</v>
+        <v>38972501</v>
       </c>
       <c r="B178" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="C178">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D178" t="s">
         <v>522</v>
@@ -15746,27 +15755,21 @@
         <v>1</v>
       </c>
       <c r="I178" t="s">
-        <v>523</v>
-      </c>
-      <c r="J178" t="s">
-        <v>706</v>
+        <v>527</v>
       </c>
       <c r="K178" t="s">
-        <v>592</v>
-      </c>
-      <c r="L178" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179">
-        <v>33095447</v>
+        <v>35099770</v>
       </c>
       <c r="B179" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="C179">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D179" t="s">
         <v>522</v>
@@ -15784,19 +15787,16 @@
         <v>1</v>
       </c>
       <c r="I179" t="s">
-        <v>523</v>
-      </c>
-      <c r="J179" t="s">
-        <v>707</v>
+        <v>527</v>
       </c>
       <c r="K179" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="L179" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>40533884</v>
       </c>
@@ -15844,14 +15844,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219E930B-1299-6144-BA90-D153D9BBD12D}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>708</v>
       </c>
@@ -15868,7 +15868,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>713</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>715</v>
       </c>
@@ -15890,7 +15890,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>717</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>719</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>721</v>
       </c>
@@ -15923,7 +15923,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>723</v>
       </c>
@@ -15934,31 +15934,31 @@
         <v>724</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>725</v>
       </c>
       <c r="B8">
         <f>COUNTIF(PRISMA_log!F2:F180,"exclude")</f>
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>726</v>
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>728</v>
       </c>
@@ -15969,19 +15969,19 @@
         <v>729</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>730</v>
       </c>
       <c r="B11">
         <f>B9</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>732</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>734</v>
       </c>
@@ -16005,7 +16005,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>736</v>
       </c>
@@ -16013,7 +16013,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>738</v>
       </c>
@@ -16029,12 +16029,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E88733E-5FDC-0E4C-BD4F-5C62F44A6D93}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>506</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>507</v>
       </c>
@@ -16050,12 +16050,12 @@
         <v>485</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>509</v>
       </c>
@@ -16066,17 +16066,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f38dbe94-7885-4da3-8834-2d39cad2d886" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca24d7f-b98d-43a3-b659-e3037fc904a8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001DF9BD4C136BCB48BFFAEB204B48DBA3" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81104982f69df3422b2ca7147b1d7166">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca24d7f-b98d-43a3-b659-e3037fc904a8" xmlns:ns3="f38dbe94-7885-4da3-8834-2d39cad2d886" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d038e88f27c07df9ba953a0dee2d397" ns2:_="" ns3:_="">
     <xsd:import namespace="cca24d7f-b98d-43a3-b659-e3037fc904a8"/>
@@ -16305,7 +16294,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -16314,24 +16303,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4925C41-A671-4894-A7EC-74D2C9B91DB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="f38dbe94-7885-4da3-8834-2d39cad2d886"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="cca24d7f-b98d-43a3-b659-e3037fc904a8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f38dbe94-7885-4da3-8834-2d39cad2d886" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca24d7f-b98d-43a3-b659-e3037fc904a8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE09A24E-24A0-461F-BA50-0F15CA18E539}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16350,10 +16333,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B4BE05D-44F4-41EF-986B-2153430D3700}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4925C41-A671-4894-A7EC-74D2C9B91DB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="f38dbe94-7885-4da3-8834-2d39cad2d886"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="cca24d7f-b98d-43a3-b659-e3037fc904a8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/raw/pubmed_query_results.xlsx
+++ b/data/raw/pubmed_query_results.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB433FD-CE9C-7F49-B8D5-4805EE3CC0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="46080" windowHeight="25320" activeTab="1" xr2:uid="{36482912-1EB2-2645-8039-9AB186E00228}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="46080" windowHeight="25320" xr2:uid="{36482912-1EB2-2645-8039-9AB186E00228}"/>
   </bookViews>
   <sheets>
     <sheet name="pubmed_query_results" sheetId="1" r:id="rId1"/>
@@ -2277,7 +2277,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3149,7 +3149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56771020-6714-E84A-8EBC-56D37C28F631}">
   <dimension ref="A1:H180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="45.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
@@ -3158,7 +3158,7 @@
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="34">
       <c r="A2">
         <v>33532864</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="34">
       <c r="A3">
         <v>37400792</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="17">
       <c r="A4">
         <v>37261792</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="34">
       <c r="A5">
         <v>36573973</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="34">
       <c r="A6">
         <v>34264297</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="51">
       <c r="A7">
         <v>33437033</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="51">
       <c r="A8">
         <v>33226606</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="51">
       <c r="A9">
         <v>37794564</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="34">
       <c r="A10">
         <v>32939031</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="51">
       <c r="A11">
         <v>32450155</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="51">
       <c r="A12">
         <v>35368817</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="51">
       <c r="A13">
         <v>38972501</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="34">
       <c r="A14">
         <v>38797326</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="34">
       <c r="A15">
         <v>38104198</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="34">
       <c r="A16">
         <v>37126668</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="34">
       <c r="A17">
         <v>38671320</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="34">
       <c r="A18">
         <v>35229136</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="17">
       <c r="A19">
         <v>32739203</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="34">
       <c r="A20">
         <v>36753701</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="34">
       <c r="A21">
         <v>35994232</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="51">
       <c r="A22">
         <v>39138396</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="51">
       <c r="A23">
         <v>34237823</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="34">
       <c r="A24">
         <v>34519781</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="34">
       <c r="A25">
         <v>32646915</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="51">
       <c r="A26">
         <v>38190104</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="68">
       <c r="A27">
         <v>36623684</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="34">
       <c r="A28">
         <v>36444934</v>
       </c>
@@ -3679,7 +3679,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="51">
       <c r="A29">
         <v>38852815</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="34">
       <c r="A30">
         <v>37270787</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="34">
       <c r="A31">
         <v>35115544</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="34">
       <c r="A32">
         <v>32312792</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="34">
       <c r="A33">
         <v>31853010</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="34">
       <c r="A34">
         <v>34067580</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="51">
       <c r="A35">
         <v>37624678</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="51">
       <c r="A36">
         <v>37103770</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="51">
       <c r="A37">
         <v>39405682</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="51">
       <c r="A38">
         <v>39402708</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="51">
       <c r="A39">
         <v>37489581</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="51">
       <c r="A40">
         <v>38905995</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="68">
       <c r="A41">
         <v>39819994</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="34">
       <c r="A42">
         <v>33783510</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="34">
       <c r="A43">
         <v>36245662</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="34">
       <c r="A44">
         <v>32889981</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="34">
       <c r="A45">
         <v>36525551</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="51">
       <c r="A46">
         <v>40345499</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="17">
       <c r="A47">
         <v>31822006</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="68">
       <c r="A48">
         <v>40484353</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="34">
       <c r="A49">
         <v>32799815</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="34">
       <c r="A50">
         <v>36758113</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="34">
       <c r="A51">
         <v>34449333</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="51">
       <c r="A52">
         <v>35120996</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="34">
       <c r="A53">
         <v>32855195</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="51">
       <c r="A54">
         <v>34946851</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="51">
       <c r="A55">
         <v>35006361</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="34">
       <c r="A56">
         <v>34343338</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="34">
       <c r="A57">
         <v>34363274</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="51">
       <c r="A58">
         <v>37391705</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="51">
       <c r="A59">
         <v>32080893</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="34">
       <c r="A60">
         <v>33276865</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="51">
       <c r="A61">
         <v>32574212</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="51">
       <c r="A62">
         <v>37248651</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="85">
       <c r="A63">
         <v>37510393</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="68">
       <c r="A64">
         <v>40325148</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ht="51">
       <c r="A65">
         <v>35962481</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ht="51">
       <c r="A66">
         <v>36404353</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="68">
       <c r="A67">
         <v>36072369</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ht="51">
       <c r="A68">
         <v>35099770</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ht="68">
       <c r="A69">
         <v>35393322</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ht="51">
       <c r="A70">
         <v>35148957</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ht="51">
       <c r="A71">
         <v>39054238</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" ht="51">
       <c r="A72">
         <v>33838163</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="34">
       <c r="A73">
         <v>37229630</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ht="51">
       <c r="A74">
         <v>36949158</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ht="51">
       <c r="A75">
         <v>37759214</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="68">
       <c r="A76">
         <v>39965361</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ht="51">
       <c r="A77">
         <v>37978231</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ht="51">
       <c r="A78">
         <v>37037154</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ht="68">
       <c r="A79">
         <v>38022507</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ht="51">
       <c r="A80">
         <v>34354814</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="51">
       <c r="A81">
         <v>36627639</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="51">
       <c r="A82">
         <v>33108403</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="51">
       <c r="A83">
         <v>38152017</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="34">
       <c r="A84">
         <v>35603906</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="51">
       <c r="A85">
         <v>33095447</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="68">
       <c r="A86">
         <v>34521993</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="34">
       <c r="A87">
         <v>36688940</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ht="68">
       <c r="A88">
         <v>35980750</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="51">
       <c r="A89">
         <v>34946941</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" ht="51">
       <c r="A90">
         <v>31646670</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="51">
       <c r="A91">
         <v>34545573</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="51">
       <c r="A92">
         <v>39333970</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="68">
       <c r="A93">
         <v>34134020</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="51">
       <c r="A94">
         <v>34565606</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="51">
       <c r="A95">
         <v>32029730</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="68">
       <c r="A96">
         <v>35064937</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" ht="68">
       <c r="A97">
         <v>36463540</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" ht="51">
       <c r="A98">
         <v>32398770</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" ht="17">
       <c r="A99">
         <v>33958773</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" ht="68">
       <c r="A100">
         <v>38347632</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" ht="51">
       <c r="A101">
         <v>34148064</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" ht="34">
       <c r="A102">
         <v>34327334</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" ht="51">
       <c r="A103">
         <v>37042117</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" ht="51">
       <c r="A104">
         <v>39150521</v>
       </c>
@@ -4989,7 +4989,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" ht="51">
       <c r="A105">
         <v>35369652</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" ht="34">
       <c r="A106">
         <v>38906652</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" ht="51">
       <c r="A107">
         <v>35244702</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" ht="51">
       <c r="A108">
         <v>39363241</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" ht="34">
       <c r="A109">
         <v>32299846</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" ht="51">
       <c r="A110">
         <v>32779812</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" ht="51">
       <c r="A111">
         <v>39626636</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" ht="68">
       <c r="A112">
         <v>38932496</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="68">
       <c r="A113">
         <v>33407230</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="34">
       <c r="A114">
         <v>37864521</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="68">
       <c r="A115">
         <v>33693791</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ht="51">
       <c r="A116">
         <v>32969247</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="68">
       <c r="A117">
         <v>35429337</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="51">
       <c r="A118">
         <v>38547852</v>
       </c>
@@ -5227,7 +5227,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="68">
       <c r="A119">
         <v>39143076</v>
       </c>
@@ -5244,7 +5244,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="68">
       <c r="A120">
         <v>37228720</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="34">
       <c r="A121">
         <v>34628264</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="68">
       <c r="A122">
         <v>36547129</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="51">
       <c r="A123">
         <v>40533884</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="68">
       <c r="A124">
         <v>34923958</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="34">
       <c r="A125">
         <v>39832277</v>
       </c>
@@ -5349,7 +5349,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="51">
       <c r="A126">
         <v>31999492</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="34">
       <c r="A127">
         <v>32723786</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="68">
       <c r="A128">
         <v>33107440</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" ht="102">
       <c r="A129">
         <v>30953057</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" ht="68">
       <c r="A130">
         <v>37468236</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" ht="34">
       <c r="A131">
         <v>32803290</v>
       </c>
@@ -5451,7 +5451,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" ht="85">
       <c r="A132">
         <v>38609702</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" ht="68">
       <c r="A133">
         <v>32600054</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" ht="34">
       <c r="A134">
         <v>32828237</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" ht="85">
       <c r="A135">
         <v>39107157</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" ht="34">
       <c r="A136">
         <v>33534524</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" ht="68">
       <c r="A137">
         <v>34197840</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" ht="51">
       <c r="A138">
         <v>32334565</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" ht="51">
       <c r="A139">
         <v>36782285</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" ht="68">
       <c r="A140">
         <v>35314744</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" ht="51">
       <c r="A141">
         <v>38574989</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" ht="51">
       <c r="A142">
         <v>31852011</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" ht="51">
       <c r="A143">
         <v>33107222</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="51">
       <c r="A144">
         <v>31992108</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="51">
       <c r="A145">
         <v>32661119</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" ht="51">
       <c r="A146">
         <v>38678107</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" ht="34">
       <c r="A147">
         <v>37574436</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" ht="68">
       <c r="A148">
         <v>34237133</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" ht="34">
       <c r="A149">
         <v>33087822</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" ht="68">
       <c r="A150">
         <v>33861738</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" ht="51">
       <c r="A151">
         <v>33048330</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" ht="68">
       <c r="A152">
         <v>32673684</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" ht="51">
       <c r="A153">
         <v>35977080</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" ht="85">
       <c r="A154">
         <v>38886300</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" ht="68">
       <c r="A155">
         <v>34358382</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" ht="51">
       <c r="A156">
         <v>34654685</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" ht="51">
       <c r="A157">
         <v>32176594</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" ht="51">
       <c r="A158">
         <v>39913368</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" ht="51">
       <c r="A159">
         <v>37349938</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" ht="68">
       <c r="A160">
         <v>31764220</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" ht="34">
       <c r="A161">
         <v>36253912</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" ht="68">
       <c r="A162">
         <v>35763031</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" ht="85">
       <c r="A163">
         <v>35655039</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" ht="51">
       <c r="A164">
         <v>35264217</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" ht="51">
       <c r="A165">
         <v>33111320</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" ht="68">
       <c r="A166">
         <v>32968206</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" ht="51">
       <c r="A167">
         <v>31513279</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" ht="85">
       <c r="A168">
         <v>37358729</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" ht="51">
       <c r="A169">
         <v>35017463</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" ht="51">
       <c r="A170">
         <v>38032814</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" ht="51">
       <c r="A171">
         <v>32060504</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="172" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" ht="51">
       <c r="A172">
         <v>34980496</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" ht="68">
       <c r="A173">
         <v>38327067</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="174" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" ht="51">
       <c r="A174">
         <v>36292688</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="175" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" ht="51">
       <c r="A175">
         <v>32659871</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" ht="17">
       <c r="A176">
         <v>32358593</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="177" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" ht="51">
       <c r="A177">
         <v>38752978</v>
       </c>
@@ -6233,7 +6233,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="178" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" ht="34">
       <c r="A178">
         <v>33275263</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" ht="51">
       <c r="A179">
         <v>32211780</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" ht="51">
       <c r="A180">
         <v>34558169</v>
       </c>
@@ -6293,7 +6293,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73CCE44A-5414-404E-A419-00AC61B8F7E5}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:N180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
@@ -6308,7 +6308,7 @@
     <col min="14" max="14" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="34" hidden="1">
       <c r="A2">
         <v>33532864</v>
       </c>
@@ -6371,7 +6371,7 @@
       <c r="L2"/>
       <c r="M2"/>
     </row>
-    <row r="3" spans="1:14" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="17" hidden="1">
       <c r="A3">
         <v>37400792</v>
       </c>
@@ -6390,7 +6390,7 @@
       <c r="L3"/>
       <c r="M3"/>
     </row>
-    <row r="4" spans="1:14" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="17" hidden="1">
       <c r="A4">
         <v>37261792</v>
       </c>
@@ -6409,7 +6409,7 @@
       <c r="L4"/>
       <c r="M4"/>
     </row>
-    <row r="5" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="34" hidden="1">
       <c r="A5">
         <v>36573973</v>
       </c>
@@ -6431,7 +6431,7 @@
       <c r="L5"/>
       <c r="M5"/>
     </row>
-    <row r="6" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="34" hidden="1">
       <c r="A6">
         <v>34264297</v>
       </c>
@@ -6450,7 +6450,7 @@
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="34" hidden="1">
       <c r="A7">
         <v>33437033</v>
       </c>
@@ -6472,7 +6472,7 @@
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="51">
       <c r="A8">
         <v>33226606</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="119">
       <c r="A9">
         <v>37794564</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="34">
       <c r="A10">
         <v>32939031</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="51" hidden="1">
       <c r="A11">
         <v>32450155</v>
       </c>
@@ -6623,7 +6623,7 @@
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="51" hidden="1">
       <c r="A12">
         <v>35368817</v>
       </c>
@@ -6645,7 +6645,7 @@
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="34">
       <c r="A13">
         <v>38972501</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="34" hidden="1">
       <c r="A14">
         <v>38797326</v>
       </c>
@@ -6705,7 +6705,7 @@
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="34" hidden="1">
       <c r="A15">
         <v>38104198</v>
       </c>
@@ -6724,7 +6724,7 @@
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="34" hidden="1">
       <c r="A16">
         <v>37126668</v>
       </c>
@@ -6743,7 +6743,7 @@
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="34" hidden="1">
       <c r="A17">
         <v>38671320</v>
       </c>
@@ -6762,7 +6762,7 @@
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="34" hidden="1">
       <c r="A18">
         <v>35229136</v>
       </c>
@@ -6781,7 +6781,7 @@
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="17">
       <c r="A19">
         <v>32739203</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="34">
       <c r="A20">
         <v>36753701</v>
       </c>
@@ -6839,7 +6839,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="34" hidden="1">
       <c r="A21">
         <v>35994232</v>
       </c>
@@ -6858,7 +6858,7 @@
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="34" hidden="1">
       <c r="A22">
         <v>39138396</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="34" hidden="1">
       <c r="A23">
         <v>34237823</v>
       </c>
@@ -6899,7 +6899,7 @@
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="34" hidden="1">
       <c r="A24">
         <v>34519781</v>
       </c>
@@ -6918,7 +6918,7 @@
       <c r="L24"/>
       <c r="M24"/>
     </row>
-    <row r="25" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="34">
       <c r="A25">
         <v>32646915</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="51" hidden="1">
       <c r="A26">
         <v>38190104</v>
       </c>
@@ -6963,7 +6963,7 @@
       <c r="L26"/>
       <c r="M26"/>
     </row>
-    <row r="27" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="51" hidden="1">
       <c r="A27">
         <v>36623684</v>
       </c>
@@ -6982,7 +6982,7 @@
       <c r="L27"/>
       <c r="M27"/>
     </row>
-    <row r="28" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="34" hidden="1">
       <c r="A28">
         <v>36444934</v>
       </c>
@@ -7001,7 +7001,7 @@
       <c r="L28"/>
       <c r="M28"/>
     </row>
-    <row r="29" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="51" hidden="1">
       <c r="A29">
         <v>38852815</v>
       </c>
@@ -7020,7 +7020,7 @@
       <c r="L29"/>
       <c r="M29"/>
     </row>
-    <row r="30" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="34">
       <c r="A30">
         <v>37270787</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="34" hidden="1">
       <c r="A31">
         <v>35115544</v>
       </c>
@@ -7071,7 +7071,7 @@
       <c r="L31"/>
       <c r="M31"/>
     </row>
-    <row r="32" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="34" hidden="1">
       <c r="A32">
         <v>32312792</v>
       </c>
@@ -7093,7 +7093,7 @@
       <c r="L32"/>
       <c r="M32"/>
     </row>
-    <row r="33" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="34" hidden="1">
       <c r="A33">
         <v>31853010</v>
       </c>
@@ -7112,7 +7112,7 @@
       <c r="L33"/>
       <c r="M33"/>
     </row>
-    <row r="34" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="34" hidden="1">
       <c r="A34">
         <v>34067580</v>
       </c>
@@ -7131,7 +7131,7 @@
       <c r="L34"/>
       <c r="M34"/>
     </row>
-    <row r="35" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="51" hidden="1">
       <c r="A35">
         <v>37624678</v>
       </c>
@@ -7150,7 +7150,7 @@
       <c r="L35"/>
       <c r="M35"/>
     </row>
-    <row r="36" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="34" hidden="1">
       <c r="A36">
         <v>37103770</v>
       </c>
@@ -7169,7 +7169,7 @@
       <c r="L36"/>
       <c r="M36"/>
     </row>
-    <row r="37" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="51" hidden="1">
       <c r="A37">
         <v>39405682</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="L37"/>
       <c r="M37"/>
     </row>
-    <row r="38" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="51" hidden="1">
       <c r="A38">
         <v>39402708</v>
       </c>
@@ -7207,7 +7207,7 @@
       <c r="L38"/>
       <c r="M38"/>
     </row>
-    <row r="39" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="34">
       <c r="A39">
         <v>37489581</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="51" hidden="1">
       <c r="A40">
         <v>38905995</v>
       </c>
@@ -7252,7 +7252,7 @@
       <c r="L40"/>
       <c r="M40"/>
     </row>
-    <row r="41" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="51" hidden="1">
       <c r="A41">
         <v>39819994</v>
       </c>
@@ -7271,7 +7271,7 @@
       <c r="L41"/>
       <c r="M41"/>
     </row>
-    <row r="42" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="34" hidden="1">
       <c r="A42">
         <v>33783510</v>
       </c>
@@ -7290,7 +7290,7 @@
       <c r="L42"/>
       <c r="M42"/>
     </row>
-    <row r="43" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="34" hidden="1">
       <c r="A43">
         <v>36245662</v>
       </c>
@@ -7309,7 +7309,7 @@
       <c r="L43"/>
       <c r="M43"/>
     </row>
-    <row r="44" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="34" hidden="1">
       <c r="A44">
         <v>32889981</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="L44"/>
       <c r="M44"/>
     </row>
-    <row r="45" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="34" hidden="1">
       <c r="A45">
         <v>36525551</v>
       </c>
@@ -7347,7 +7347,7 @@
       <c r="L45"/>
       <c r="M45"/>
     </row>
-    <row r="46" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="51" hidden="1">
       <c r="A46">
         <v>40345499</v>
       </c>
@@ -7366,7 +7366,7 @@
       <c r="L46"/>
       <c r="M46"/>
     </row>
-    <row r="47" spans="1:14" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="17" hidden="1">
       <c r="A47">
         <v>31822006</v>
       </c>
@@ -7385,7 +7385,7 @@
       <c r="L47"/>
       <c r="M47"/>
     </row>
-    <row r="48" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="68" hidden="1">
       <c r="A48">
         <v>40484353</v>
       </c>
@@ -7404,7 +7404,7 @@
       <c r="L48"/>
       <c r="M48"/>
     </row>
-    <row r="49" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A49">
         <v>32799815</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="50" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A50">
         <v>36758113</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A51">
         <v>34449333</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="52" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A52">
         <v>35120996</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="53" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A53">
         <v>32855195</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="54" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A54">
         <v>34946851</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="55" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A55">
         <v>35006361</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="56" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A56">
         <v>34343338</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="57" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A57">
         <v>34363274</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="58" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A58">
         <v>37391705</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="59" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A59">
         <v>32080893</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="60" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A60">
         <v>33276865</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="61" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A61">
         <v>32574212</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="62" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A62">
         <v>37248651</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="63" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A63">
         <v>37510393</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="64" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A64">
         <v>40325148</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="51" hidden="1">
       <c r="A65">
         <v>35962481</v>
       </c>
@@ -7695,7 +7695,7 @@
       <c r="L65"/>
       <c r="M65"/>
     </row>
-    <row r="66" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="51" hidden="1">
       <c r="A66">
         <v>36404353</v>
       </c>
@@ -7714,7 +7714,7 @@
       <c r="L66"/>
       <c r="M66"/>
     </row>
-    <row r="67" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="51" hidden="1">
       <c r="A67">
         <v>36072369</v>
       </c>
@@ -7733,7 +7733,7 @@
       <c r="L67"/>
       <c r="M67"/>
     </row>
-    <row r="68" spans="1:14" ht="68" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="68">
       <c r="A68">
         <v>35099770</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="51">
       <c r="A69">
         <v>35393322</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="51" hidden="1">
       <c r="A70">
         <v>35148957</v>
       </c>
@@ -7825,7 +7825,7 @@
       <c r="L70"/>
       <c r="M70"/>
     </row>
-    <row r="71" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="34" hidden="1">
       <c r="A71">
         <v>39054238</v>
       </c>
@@ -7844,7 +7844,7 @@
       <c r="L71"/>
       <c r="M71"/>
     </row>
-    <row r="72" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="34" hidden="1">
       <c r="A72">
         <v>33838163</v>
       </c>
@@ -7863,7 +7863,7 @@
       <c r="L72"/>
       <c r="M72"/>
     </row>
-    <row r="73" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="34" hidden="1">
       <c r="A73">
         <v>37229630</v>
       </c>
@@ -7882,7 +7882,7 @@
       <c r="L73"/>
       <c r="M73"/>
     </row>
-    <row r="74" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="51" hidden="1">
       <c r="A74">
         <v>36949158</v>
       </c>
@@ -7901,7 +7901,7 @@
       <c r="L74"/>
       <c r="M74"/>
     </row>
-    <row r="75" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="51" hidden="1">
       <c r="A75">
         <v>37759214</v>
       </c>
@@ -7920,7 +7920,7 @@
       <c r="L75"/>
       <c r="M75"/>
     </row>
-    <row r="76" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="51" hidden="1">
       <c r="A76">
         <v>39965361</v>
       </c>
@@ -7939,7 +7939,7 @@
       <c r="L76"/>
       <c r="M76"/>
     </row>
-    <row r="77" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="51" hidden="1">
       <c r="A77">
         <v>37978231</v>
       </c>
@@ -7958,7 +7958,7 @@
       <c r="L77"/>
       <c r="M77"/>
     </row>
-    <row r="78" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="51" hidden="1">
       <c r="A78">
         <v>37037154</v>
       </c>
@@ -7977,7 +7977,7 @@
       <c r="L78"/>
       <c r="M78"/>
     </row>
-    <row r="79" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="68" hidden="1">
       <c r="A79">
         <v>38022507</v>
       </c>
@@ -7996,7 +7996,7 @@
       <c r="L79"/>
       <c r="M79"/>
     </row>
-    <row r="80" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="51" hidden="1">
       <c r="A80">
         <v>34354814</v>
       </c>
@@ -8015,7 +8015,7 @@
       <c r="L80"/>
       <c r="M80"/>
     </row>
-    <row r="81" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" ht="51" hidden="1">
       <c r="A81">
         <v>36627639</v>
       </c>
@@ -8034,7 +8034,7 @@
       <c r="L81"/>
       <c r="M81"/>
     </row>
-    <row r="82" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" ht="51" hidden="1">
       <c r="A82">
         <v>33108403</v>
       </c>
@@ -8053,7 +8053,7 @@
       <c r="L82"/>
       <c r="M82"/>
     </row>
-    <row r="83" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" ht="51" hidden="1">
       <c r="A83">
         <v>38152017</v>
       </c>
@@ -8072,7 +8072,7 @@
       <c r="L83"/>
       <c r="M83"/>
     </row>
-    <row r="84" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" ht="34" hidden="1">
       <c r="A84">
         <v>35603906</v>
       </c>
@@ -8091,7 +8091,7 @@
       <c r="L84"/>
       <c r="M84"/>
     </row>
-    <row r="85" spans="1:14" ht="34" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" ht="34">
       <c r="A85">
         <v>33095447</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" ht="51" hidden="1">
       <c r="A86">
         <v>34521993</v>
       </c>
@@ -8136,7 +8136,7 @@
       <c r="L86"/>
       <c r="M86"/>
     </row>
-    <row r="87" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" ht="34" hidden="1">
       <c r="A87">
         <v>36688940</v>
       </c>
@@ -8155,7 +8155,7 @@
       <c r="L87"/>
       <c r="M87"/>
     </row>
-    <row r="88" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" ht="68" hidden="1">
       <c r="A88">
         <v>35980750</v>
       </c>
@@ -8174,7 +8174,7 @@
       <c r="L88"/>
       <c r="M88"/>
     </row>
-    <row r="89" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" ht="51" hidden="1">
       <c r="A89">
         <v>34946941</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="L89"/>
       <c r="M89"/>
     </row>
-    <row r="90" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" ht="51" hidden="1">
       <c r="A90">
         <v>31646670</v>
       </c>
@@ -8212,7 +8212,7 @@
       <c r="L90"/>
       <c r="M90"/>
     </row>
-    <row r="91" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" ht="34" hidden="1">
       <c r="A91">
         <v>34545573</v>
       </c>
@@ -8231,7 +8231,7 @@
       <c r="L91"/>
       <c r="M91"/>
     </row>
-    <row r="92" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" ht="51" hidden="1">
       <c r="A92">
         <v>39333970</v>
       </c>
@@ -8250,7 +8250,7 @@
       <c r="L92"/>
       <c r="M92"/>
     </row>
-    <row r="93" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" ht="51" hidden="1">
       <c r="A93">
         <v>34134020</v>
       </c>
@@ -8269,7 +8269,7 @@
       <c r="L93"/>
       <c r="M93"/>
     </row>
-    <row r="94" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" ht="51" hidden="1">
       <c r="A94">
         <v>34565606</v>
       </c>
@@ -8288,7 +8288,7 @@
       <c r="L94"/>
       <c r="M94"/>
     </row>
-    <row r="95" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" ht="34" hidden="1">
       <c r="A95">
         <v>32029730</v>
       </c>
@@ -8307,7 +8307,7 @@
       <c r="L95"/>
       <c r="M95"/>
     </row>
-    <row r="96" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" ht="51" hidden="1">
       <c r="A96">
         <v>35064937</v>
       </c>
@@ -8326,7 +8326,7 @@
       <c r="L96"/>
       <c r="M96"/>
     </row>
-    <row r="97" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A97">
         <v>36463540</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="98" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A98">
         <v>32398770</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="99" spans="1:5" customFormat="1" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" customFormat="1" ht="17" hidden="1">
       <c r="A99">
         <v>33958773</v>
       </c>
@@ -8377,7 +8377,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="100" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A100">
         <v>38347632</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A101">
         <v>34148064</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="102" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A102">
         <v>34327334</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="103" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A103">
         <v>37042117</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A104">
         <v>39150521</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A105">
         <v>35369652</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="106" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A106">
         <v>38906652</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A107">
         <v>35244702</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="108" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A108">
         <v>39363241</v>
       </c>
@@ -8530,7 +8530,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A109">
         <v>32299846</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="110" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A110">
         <v>32779812</v>
       </c>
@@ -8564,7 +8564,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="111" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A111">
         <v>39626636</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A112">
         <v>38932496</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" ht="51" hidden="1">
       <c r="A113">
         <v>33407230</v>
       </c>
@@ -8617,7 +8617,7 @@
       <c r="L113"/>
       <c r="M113"/>
     </row>
-    <row r="114" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" ht="34" hidden="1">
       <c r="A114">
         <v>37864521</v>
       </c>
@@ -8636,7 +8636,7 @@
       <c r="L114"/>
       <c r="M114"/>
     </row>
-    <row r="115" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" ht="68" hidden="1">
       <c r="A115">
         <v>33693791</v>
       </c>
@@ -8655,7 +8655,7 @@
       <c r="L115"/>
       <c r="M115"/>
     </row>
-    <row r="116" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" ht="34" hidden="1">
       <c r="A116">
         <v>32969247</v>
       </c>
@@ -8674,7 +8674,7 @@
       <c r="L116"/>
       <c r="M116"/>
     </row>
-    <row r="117" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" ht="68" hidden="1">
       <c r="A117">
         <v>35429337</v>
       </c>
@@ -8693,7 +8693,7 @@
       <c r="L117"/>
       <c r="M117"/>
     </row>
-    <row r="118" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" ht="51" hidden="1">
       <c r="A118">
         <v>38547852</v>
       </c>
@@ -8712,7 +8712,7 @@
       <c r="L118"/>
       <c r="M118"/>
     </row>
-    <row r="119" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" ht="51" hidden="1">
       <c r="A119">
         <v>39143076</v>
       </c>
@@ -8731,7 +8731,7 @@
       <c r="L119"/>
       <c r="M119"/>
     </row>
-    <row r="120" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" ht="68" hidden="1">
       <c r="A120">
         <v>37228720</v>
       </c>
@@ -8750,7 +8750,7 @@
       <c r="L120"/>
       <c r="M120"/>
     </row>
-    <row r="121" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" ht="34" hidden="1">
       <c r="A121">
         <v>34628264</v>
       </c>
@@ -8769,7 +8769,7 @@
       <c r="L121"/>
       <c r="M121"/>
     </row>
-    <row r="122" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" ht="51" hidden="1">
       <c r="A122">
         <v>36547129</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="L122"/>
       <c r="M122"/>
     </row>
-    <row r="123" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" ht="51">
       <c r="A123">
         <v>40533884</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" ht="68" hidden="1">
       <c r="A124">
         <v>34923958</v>
       </c>
@@ -8851,7 +8851,7 @@
       <c r="L124"/>
       <c r="M124"/>
     </row>
-    <row r="125" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" ht="34" hidden="1">
       <c r="A125">
         <v>39832277</v>
       </c>
@@ -8870,7 +8870,7 @@
       <c r="L125"/>
       <c r="M125"/>
     </row>
-    <row r="126" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" ht="51" hidden="1">
       <c r="A126">
         <v>31999492</v>
       </c>
@@ -8889,7 +8889,7 @@
       <c r="L126"/>
       <c r="M126"/>
     </row>
-    <row r="127" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" ht="34" hidden="1">
       <c r="A127">
         <v>32723786</v>
       </c>
@@ -8908,7 +8908,7 @@
       <c r="L127"/>
       <c r="M127"/>
     </row>
-    <row r="128" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" ht="51" hidden="1">
       <c r="A128">
         <v>33107440</v>
       </c>
@@ -8927,7 +8927,7 @@
       <c r="L128"/>
       <c r="M128"/>
     </row>
-    <row r="129" spans="1:5" customFormat="1" ht="85" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" customFormat="1" ht="85" hidden="1">
       <c r="A129">
         <v>30953057</v>
       </c>
@@ -8944,7 +8944,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="130" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A130">
         <v>37468236</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="131" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A131">
         <v>32803290</v>
       </c>
@@ -8978,7 +8978,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="132" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A132">
         <v>38609702</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="133" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A133">
         <v>32600054</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="134" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A134">
         <v>32828237</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="135" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A135">
         <v>39107157</v>
       </c>
@@ -9046,7 +9046,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="136" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A136">
         <v>33534524</v>
       </c>
@@ -9063,7 +9063,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="137" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A137">
         <v>34197840</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="138" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A138">
         <v>32334565</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="139" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A139">
         <v>36782285</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="140" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A140">
         <v>35314744</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="141" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A141">
         <v>38574989</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="142" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A142">
         <v>31852011</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="143" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A143">
         <v>33107222</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="144" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A144">
         <v>31992108</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="145" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A145">
         <v>32661119</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="146" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A146">
         <v>38678107</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="147" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A147">
         <v>37574436</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="148" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A148">
         <v>34237133</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="149" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A149">
         <v>33087822</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="150" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A150">
         <v>33861738</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="151" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A151">
         <v>33048330</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="152" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A152">
         <v>32673684</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="153" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A153">
         <v>35977080</v>
       </c>
@@ -9352,7 +9352,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="154" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A154">
         <v>38886300</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="155" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A155">
         <v>34358382</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="156" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A156">
         <v>34654685</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="157" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A157">
         <v>32176594</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="158" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A158">
         <v>39913368</v>
       </c>
@@ -9437,7 +9437,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="159" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A159">
         <v>37349938</v>
       </c>
@@ -9454,7 +9454,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="160" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A160">
         <v>31764220</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="161" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A161">
         <v>36253912</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="162" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A162">
         <v>35763031</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="163" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A163">
         <v>35655039</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="164" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A164">
         <v>35264217</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="165" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A165">
         <v>33111320</v>
       </c>
@@ -9556,7 +9556,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="166" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A166">
         <v>32968206</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="167" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A167">
         <v>31513279</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="168" spans="1:5" customFormat="1" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:5" customFormat="1" ht="68" hidden="1">
       <c r="A168">
         <v>37358729</v>
       </c>
@@ -9607,7 +9607,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="169" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A169">
         <v>35017463</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="170" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A170">
         <v>38032814</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="171" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A171">
         <v>32060504</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="172" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A172">
         <v>34980496</v>
       </c>
@@ -9675,7 +9675,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="173" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A173">
         <v>38327067</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="174" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A174">
         <v>36292688</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="175" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A175">
         <v>32659871</v>
       </c>
@@ -9726,7 +9726,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="176" spans="1:5" customFormat="1" ht="17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" customFormat="1" ht="17" hidden="1">
       <c r="A176">
         <v>32358593</v>
       </c>
@@ -9743,7 +9743,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="177" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A177">
         <v>38752978</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="178" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A178">
         <v>33275263</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="179" spans="1:5" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:5" customFormat="1" ht="51" hidden="1">
       <c r="A179">
         <v>32211780</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="180" spans="1:5" customFormat="1" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:5" customFormat="1" ht="34" hidden="1">
       <c r="A180">
         <v>34558169</v>
       </c>
@@ -9826,14 +9826,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23894E8A-015E-5545-964F-589B1BE15133}">
   <dimension ref="A1:L180"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="50.5" customWidth="1"/>
     <col min="9" max="9" width="11.6640625" customWidth="1"/>
     <col min="10" max="10" width="33.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>510</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>33532864</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>37400792</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>37261792</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>34264297</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>38797326</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>38104198</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>37126668</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>38671320</v>
       </c>
@@ -10135,7 +10135,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>35229136</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>35994232</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>39138396</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>34519781</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>38190104</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>36623684</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>36444934</v>
       </c>
@@ -10366,7 +10366,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>38852815</v>
       </c>
@@ -10399,7 +10399,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>35115544</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>31853010</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>34067580</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>37624678</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>37103770</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>39405682</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>39402708</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>38905995</v>
       </c>
@@ -10663,7 +10663,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>39819994</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>33783510</v>
       </c>
@@ -10729,7 +10729,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>36245662</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>32889981</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>36525551</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>40345499</v>
       </c>
@@ -10861,7 +10861,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>31822006</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>40484353</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>32799815</v>
       </c>
@@ -10960,7 +10960,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>36758113</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>34449333</v>
       </c>
@@ -11026,7 +11026,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>35120996</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>32855195</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>34946851</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>35006361</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>34343338</v>
       </c>
@@ -11191,7 +11191,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>34363274</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>37391705</v>
       </c>
@@ -11257,7 +11257,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>32080893</v>
       </c>
@@ -11290,7 +11290,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>33276865</v>
       </c>
@@ -11323,7 +11323,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>32574212</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>37248651</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>37510393</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>40325148</v>
       </c>
@@ -11455,7 +11455,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>35962481</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>36404353</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>36072369</v>
       </c>
@@ -11554,7 +11554,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>35148957</v>
       </c>
@@ -11587,7 +11587,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>39054238</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>33838163</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11">
       <c r="A56">
         <v>37229630</v>
       </c>
@@ -11686,7 +11686,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>36949158</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11">
       <c r="A58">
         <v>37759214</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>39965361</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>37978231</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>37037154</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62">
         <v>38022507</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>34354814</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>36627639</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>33108403</v>
       </c>
@@ -11983,7 +11983,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11">
       <c r="A66">
         <v>38152017</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67">
         <v>35603906</v>
       </c>
@@ -12049,7 +12049,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68">
         <v>34521993</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11">
       <c r="A69">
         <v>36688940</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70">
         <v>35980750</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71">
         <v>34946941</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11">
       <c r="A72">
         <v>31646670</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73">
         <v>34545573</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74">
         <v>39333970</v>
       </c>
@@ -12280,7 +12280,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75">
         <v>34134020</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11">
       <c r="A76">
         <v>34565606</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77">
         <v>32029730</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78">
         <v>35064937</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79">
         <v>36463540</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80">
         <v>32398770</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81">
         <v>33958773</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82">
         <v>38347632</v>
       </c>
@@ -12544,7 +12544,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83">
         <v>34148064</v>
       </c>
@@ -12577,7 +12577,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84">
         <v>34327334</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85">
         <v>37042117</v>
       </c>
@@ -12643,7 +12643,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86">
         <v>39150521</v>
       </c>
@@ -12676,7 +12676,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87">
         <v>35369652</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88">
         <v>38906652</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89">
         <v>35244702</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90">
         <v>39363241</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91">
         <v>32299846</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92">
         <v>32779812</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93">
         <v>39626636</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94">
         <v>38932496</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95">
         <v>33407230</v>
       </c>
@@ -12973,7 +12973,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96">
         <v>37864521</v>
       </c>
@@ -13006,7 +13006,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97">
         <v>33693791</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11">
       <c r="A98">
         <v>32969247</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99">
         <v>35429337</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100">
         <v>38547852</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101">
         <v>39143076</v>
       </c>
@@ -13171,7 +13171,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102">
         <v>37228720</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11">
       <c r="A103">
         <v>34628264</v>
       </c>
@@ -13237,7 +13237,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104">
         <v>36547129</v>
       </c>
@@ -13270,7 +13270,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105">
         <v>34923958</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11">
       <c r="A106">
         <v>39832277</v>
       </c>
@@ -13336,7 +13336,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107">
         <v>31999492</v>
       </c>
@@ -13369,7 +13369,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108">
         <v>32723786</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11">
       <c r="A109">
         <v>33107440</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11">
       <c r="A110">
         <v>30953057</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111">
         <v>37468236</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11">
       <c r="A112">
         <v>32803290</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11">
       <c r="A113">
         <v>38609702</v>
       </c>
@@ -13567,7 +13567,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114">
         <v>32600054</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11">
       <c r="A115">
         <v>32828237</v>
       </c>
@@ -13633,7 +13633,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116">
         <v>39107157</v>
       </c>
@@ -13666,7 +13666,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117">
         <v>33534524</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11">
       <c r="A118">
         <v>34197840</v>
       </c>
@@ -13732,7 +13732,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119">
         <v>32334565</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120">
         <v>36782285</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121">
         <v>35314744</v>
       </c>
@@ -13831,7 +13831,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11">
       <c r="A122">
         <v>38574989</v>
       </c>
@@ -13864,7 +13864,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123">
         <v>31852011</v>
       </c>
@@ -13897,7 +13897,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124">
         <v>33107222</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125">
         <v>31992108</v>
       </c>
@@ -13963,7 +13963,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126">
         <v>32661119</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127">
         <v>38678107</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128">
         <v>37574436</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129">
         <v>34237133</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130">
         <v>33087822</v>
       </c>
@@ -14128,7 +14128,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131">
         <v>33861738</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132">
         <v>33048330</v>
       </c>
@@ -14194,7 +14194,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133">
         <v>32673684</v>
       </c>
@@ -14227,7 +14227,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134">
         <v>35977080</v>
       </c>
@@ -14260,7 +14260,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135">
         <v>38886300</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136">
         <v>34358382</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137">
         <v>34654685</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138">
         <v>32176594</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139">
         <v>39913368</v>
       </c>
@@ -14425,7 +14425,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140">
         <v>37349938</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141">
         <v>31764220</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142">
         <v>36253912</v>
       </c>
@@ -14524,7 +14524,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143">
         <v>35763031</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144">
         <v>35655039</v>
       </c>
@@ -14590,7 +14590,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145">
         <v>35264217</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146">
         <v>33111320</v>
       </c>
@@ -14656,7 +14656,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147">
         <v>32968206</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11">
       <c r="A148">
         <v>31513279</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149">
         <v>37358729</v>
       </c>
@@ -14755,7 +14755,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150">
         <v>35017463</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151">
         <v>38032814</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152">
         <v>32060504</v>
       </c>
@@ -14854,7 +14854,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153">
         <v>34980496</v>
       </c>
@@ -14887,7 +14887,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11">
       <c r="A154">
         <v>38327067</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11">
       <c r="A155">
         <v>36292688</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156">
         <v>32659871</v>
       </c>
@@ -14986,7 +14986,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157">
         <v>32358593</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158">
         <v>38752978</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159">
         <v>33275263</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160">
         <v>32211780</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12">
       <c r="A161">
         <v>34558169</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12">
       <c r="A162">
         <v>36573973</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12">
       <c r="A163">
         <v>33437033</v>
       </c>
@@ -15221,7 +15221,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12">
       <c r="A164">
         <v>32450155</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12">
       <c r="A165">
         <v>35368817</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12">
       <c r="A166">
         <v>34237823</v>
       </c>
@@ -15326,7 +15326,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12">
       <c r="A167">
         <v>32312792</v>
       </c>
@@ -15361,7 +15361,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12">
       <c r="A168">
         <v>32739203</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12">
       <c r="A169">
         <v>36753701</v>
       </c>
@@ -15437,7 +15437,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12">
       <c r="A170">
         <v>32646915</v>
       </c>
@@ -15475,7 +15475,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12">
       <c r="A171">
         <v>37270787</v>
       </c>
@@ -15513,7 +15513,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12">
       <c r="A172">
         <v>37489581</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12">
       <c r="A173">
         <v>35393322</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12">
       <c r="A174">
         <v>33095447</v>
       </c>
@@ -15627,7 +15627,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12">
       <c r="A175">
         <v>33226606</v>
       </c>
@@ -15659,7 +15659,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12">
       <c r="A176">
         <v>37794564</v>
       </c>
@@ -15694,7 +15694,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12">
       <c r="A177">
         <v>32939031</v>
       </c>
@@ -15729,7 +15729,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12">
       <c r="A178">
         <v>38972501</v>
       </c>
@@ -15761,7 +15761,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12">
       <c r="A179">
         <v>35099770</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12">
       <c r="A180">
         <v>40533884</v>
       </c>
@@ -15844,14 +15844,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219E930B-1299-6144-BA90-D153D9BBD12D}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="47.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>708</v>
       </c>
@@ -15868,7 +15868,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>713</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>715</v>
       </c>
@@ -15890,7 +15890,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>717</v>
       </c>
@@ -15901,7 +15901,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>719</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>721</v>
       </c>
@@ -15923,7 +15923,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>723</v>
       </c>
@@ -15934,7 +15934,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>725</v>
       </c>
@@ -15946,7 +15946,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>726</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>728</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>730</v>
       </c>
@@ -15981,7 +15981,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>732</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>734</v>
       </c>
@@ -16005,7 +16005,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>736</v>
       </c>
@@ -16013,7 +16013,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>738</v>
       </c>
@@ -16029,12 +16029,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E88733E-5FDC-0E4C-BD4F-5C62F44A6D93}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="56.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>506</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>507</v>
       </c>
@@ -16050,12 +16050,12 @@
         <v>485</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>509</v>
       </c>
@@ -16295,15 +16295,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="f38dbe94-7885-4da3-8834-2d39cad2d886" xsi:nil="true"/>
@@ -16312,6 +16303,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16334,14 +16334,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B4BE05D-44F4-41EF-986B-2153430D3700}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4925C41-A671-4894-A7EC-74D2C9B91DB2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -16356,4 +16348,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B4BE05D-44F4-41EF-986B-2153430D3700}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>